--- a/output/full_scan/batch_seq1_2026-08-27.xlsx
+++ b/output/full_scan/batch_seq1_2026-08-27.xlsx
@@ -527,74 +527,74 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1563</v>
+        <v>1303</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1040.629404870625</v>
+        <v>1221.731977696501</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>66</v>
+        <v>227.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G2" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>59.98512599959952</v>
+        <v>66.27712067864434</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>17.57465381325262</v>
+        <v>14.27292954884095</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.194834990775525</v>
+        <v>1.577692723412446</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.6475740031840054</v>
+        <v>2.073074013256329</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>817.1217477599945</v>
+        <v>1141.657201410274</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>73.40000000000001</v>
+        <v>212.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>62.16042635937127</v>
+        <v>60.0089418588019</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>20.84338468712283</v>
+        <v>18.42871108381998</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.702395125445444</v>
+        <v>3.177891799482085</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4125281086449609</v>
+        <v>1.974801202776355</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1503</v>
+        <v>1326</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>796.6572014102745</v>
+        <v>1130.066067773859</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>212.5</v>
+        <v>63.2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>60.00894183552218</v>
+        <v>57.41186657155199</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>18.42871103035161</v>
+        <v>11.61922275161804</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.177891799482085</v>
+        <v>1.521748874716579</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.974801203730332</v>
+        <v>0.3174438600498535</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1514</v>
+        <v>1301</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>789.9351260935418</v>
+        <v>1127.122361336562</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>105</v>
+        <v>63.1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>53.02168022145004</v>
+        <v>61.86856942549377</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>21.7295817123888</v>
+        <v>15.01286901438985</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.669217470582879</v>
+        <v>1.848292606064754</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,51 +729,51 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.9448556761939724</v>
+        <v>0.4324393422835992</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1326</v>
+        <v>1563</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>775.0660677738592</v>
+        <v>1040.629404870624</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>63.2</v>
+        <v>66</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>57.41186657821432</v>
+        <v>59.98512601520668</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>11.61922274716213</v>
+        <v>17.57465382401211</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.521748874716579</v>
+        <v>2.194834990775525</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.3174438600212419</v>
+        <v>0.6475740029573369</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1301</v>
+        <v>1504</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>762.122361336562</v>
+        <v>1007.121747759994</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>63.1</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,29 +817,29 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>61.86856946624197</v>
+        <v>62.16042637697635</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15.01286900398668</v>
+        <v>20.8433846985182</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.848292606064754</v>
+        <v>1.702395125445444</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4324393422835992</v>
+        <v>0.412528108482781</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>748.7943953288291</v>
+        <v>973.7943953288292</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>11.7</v>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>67.11835182662401</v>
+        <v>67.11835221232127</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>27.35173539042939</v>
+        <v>27.3517356002109</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>1.625397709442989</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.0490791418403688</v>
+        <v>0.0490791417354321</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>743.7476325356325</v>
+        <v>932.6528077180932</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>11.75</v>
+        <v>12.15</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>69.86671527661835</v>
+        <v>57.39474933790179</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>27.99735733813191</v>
+        <v>14.02358083975116</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3.974763253563252</v>
+        <v>1.693051070581144</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1682496610889425</v>
+        <v>0.0880010527019605</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1303</v>
+        <v>1514</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>741.7317153473444</v>
+        <v>924.9351260935418</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>227.5</v>
+        <v>105</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>66.27712068241325</v>
+        <v>53.02168029359571</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>14.27292948490498</v>
+        <v>21.7295817479819</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.577672847223988</v>
+        <v>2.669217470582879</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>2.073074013256329</v>
+        <v>0.9448556753353952</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1531</v>
+        <v>1316</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>738.8330562641012</v>
+        <v>903.7476325356324</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13.3</v>
+        <v>11.75</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>67.20959175829171</v>
+        <v>69.86671538539679</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>12.86531851107415</v>
+        <v>27.99735733572999</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.105258083797698</v>
+        <v>3.974763253563252</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.0285281913186391</v>
+        <v>0.168249661022164</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1519</v>
+        <v>1312</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>702.79158419595</v>
+        <v>899.5753493523324</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>770</v>
+        <v>14.3</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>63.72618067884449</v>
+        <v>71.9160416208714</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>14.56889918879554</v>
+        <v>13.57187567503218</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.664971079918188</v>
+        <v>1.708776135132687</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>7.312136832916182</v>
+        <v>0.2614153305843248</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1312</v>
+        <v>1229</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>699.5753493523324</v>
+        <v>860.9639567347255</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>14.3</v>
+        <v>42.15</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>71.91604162490501</v>
+        <v>57.13539751913282</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>13.57187565194352</v>
+        <v>16.58515242948861</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.708776135132687</v>
+        <v>0.8872316099642238</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.2614153306014973</v>
+        <v>0.1262995126468262</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1558</v>
+        <v>1519</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>619.1454996638605</v>
+        <v>843.7537449164693</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>102</v>
+        <v>770</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>64.96766377926505</v>
+        <v>63.7261807038245</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>28.58471071652634</v>
+        <v>14.56889929533127</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.916115359735214</v>
+        <v>3.739101567013312</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.5295414776284293</v>
+        <v>7.312136829672609</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1442</v>
+        <v>1528</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>618.3477141212556</v>
+        <v>842.0183594552567</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>30.25</v>
+        <v>19.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>57.13343809227274</v>
+        <v>51.92105903144837</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>24.21997899648821</v>
+        <v>27.14242776182907</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.5148165948661344</v>
+        <v>1.231049999110299</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.013212015713603</v>
+        <v>0.2269020339673996</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>607.6528077180933</v>
+        <v>830.6084086511678</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12.15</v>
+        <v>8.69</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>57.39474931522213</v>
+        <v>55.01936844302029</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>14.02358082722361</v>
+        <v>14.47520396896061</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.693051070581144</v>
+        <v>1.614466517799649</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0880010527095936</v>
+        <v>0.1139149073233776</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1440</v>
+        <v>1471</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>603.4978252224518</v>
+        <v>763.9798592151025</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>13.85</v>
+        <v>10.1</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>60.53609734880786</v>
+        <v>56.93397661487882</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>22.26450983856962</v>
+        <v>30.98333058977329</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.8259865774777684</v>
+        <v>1.692052597178324</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.060665417011288</v>
+        <v>0.1055645072816357</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1323</v>
+        <v>1531</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>598.8679970401981</v>
+        <v>738.8330562641013</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>21.3</v>
+        <v>13.3</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>58.42542874840778</v>
+        <v>67.20959300950287</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>24.42510544077968</v>
+        <v>12.86531854889706</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.5240963375536716</v>
+        <v>2.105258083797698</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.0034598233480339</v>
+        <v>0.0285281912041638</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1402</v>
+        <v>1513</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>596.7648249189947</v>
+        <v>738.6997610058277</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>28.4</v>
+        <v>170.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>53.45350841331619</v>
+        <v>58.97593575186924</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>20.97386352030738</v>
+        <v>14.54479941336398</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.465348711287517</v>
+        <v>1.784349533528658</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.1262052056666799</v>
+        <v>0.6741844005884392</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1582</v>
+        <v>1321</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>593.8058997347829</v>
+        <v>715.5332677178819</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>33.75</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>55.62726353379928</v>
+        <v>71.03594611614777</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>19.17136540135695</v>
+        <v>17.48866667766384</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.176736550014692</v>
+        <v>1.02640905040821</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.7201411877730626</v>
+        <v>0.1659868245239199</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1310</v>
+        <v>1440</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>585.6084086511678</v>
+        <v>713.4978252224519</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>8.69</v>
+        <v>13.85</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>55.01936839772992</v>
+        <v>60.53609744615564</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>14.47520392843871</v>
+        <v>22.26450978230032</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.614466517799649</v>
+        <v>0.8259865774777684</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1139149073481812</v>
+        <v>0.0606654169635891</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1236</v>
+        <v>1582</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>581.4280635804374</v>
+        <v>708.8058997347829</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>25.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>63.16286783736442</v>
+        <v>55.62726357003326</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>22.248502813354</v>
+        <v>19.17136538916012</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8116792349057793</v>
+        <v>2.176736550014692</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.0384754370193017</v>
+        <v>0.7201411874487201</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1229</v>
+        <v>1305</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>580.9639567347255</v>
+        <v>706.0874818425226</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>42.15</v>
+        <v>12.4</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>57.13539731288954</v>
+        <v>57.15365634817989</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>16.58515241632087</v>
+        <v>13.00116694251372</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.8872316099642238</v>
+        <v>2.009742403428681</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1262995126849819</v>
+        <v>0.1165132459685751</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1416</v>
+        <v>1442</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>555.2306127886944</v>
+        <v>693.3477141212556</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>11.8</v>
+        <v>30.25</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>61.94447928095606</v>
+        <v>57.13343825810211</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>31.93636262136817</v>
+        <v>24.21997900788019</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.2185719751529941</v>
+        <v>0.5148165948661344</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.03896615154171</v>
+        <v>-0.0132120159234758</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1102</v>
+        <v>1515</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>554.33036121899</v>
+        <v>683.9857363914264</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>35.1</v>
+        <v>35.4</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>63.51642034972738</v>
+        <v>56.15846079272997</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>24.82286121480965</v>
+        <v>21.52302376036273</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.6239524208363141</v>
+        <v>2.907728979571857</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.30596922001896</v>
+        <v>0.4929782232917029</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1232</v>
+        <v>1409</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>539.1810061715117</v>
+        <v>683.212255802579</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>157</v>
+        <v>25</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,49 +1824,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>55.91890229706263</v>
+        <v>56.01715613441476</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>26.67084759879961</v>
+        <v>9.510228460682924</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.3799096892105097</v>
+        <v>1.262641643686421</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.0616712534339205</v>
+        <v>0.1644461358007696</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1471</v>
+        <v>1314</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>538.9798592151025</v>
+        <v>668.0549412132126</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>10.1</v>
+        <v>8.16</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>56.93397654967772</v>
+        <v>55.16173359628412</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>30.98333063831204</v>
+        <v>16.39242345814451</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.692052597178324</v>
+        <v>1.463862551920224</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1055645073197935</v>
+        <v>0.0599375333622201</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1315</v>
+        <v>1416</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>532.2656825339631</v>
+        <v>665.2306127886944</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>65.09999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>52.37982667072396</v>
+        <v>61.94447938893094</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>33.23790370090559</v>
+        <v>31.93636262430692</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.8234504917286124</v>
+        <v>0.2185719751529941</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.044510253208291</v>
+        <v>0.0389661515226307</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1319</v>
+        <v>1102</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>529.7084122733056</v>
+        <v>664.3303612189901</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>81.7</v>
+        <v>35.1</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>58.91498751512253</v>
+        <v>63.5164203406228</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>32.75033677987024</v>
+        <v>24.82286119522626</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4348574064896122</v>
+        <v>0.6239524208363141</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,11 +2001,11 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.3739899473386225</v>
+        <v>0.3059692198758643</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>524.202705853554</v>
+        <v>656</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>15.55</v>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>78.79521109054777</v>
+        <v>78.79521112373573</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>43.30980674822013</v>
+        <v>43.30980695837568</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.9195569287343264</v>
+        <v>6.455724619275032</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.135409263777014</v>
+        <v>0.1354092637606658</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1528</v>
+        <v>1217</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>517.0183594552566</v>
+        <v>639.7049407704087</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>19.5</v>
+        <v>10</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>51.92105899253274</v>
+        <v>55.67933659401008</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>27.14242776047656</v>
+        <v>14.26590282128758</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.231049999110299</v>
+        <v>1.122606214917545</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.2269020340437175</v>
+        <v>0.0114747169443251</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1513</v>
+        <v>1441</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>513.6997610058272</v>
+        <v>631.6386713148378</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>170.5</v>
+        <v>9.15</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>58.97593569466595</v>
+        <v>56.25746653265059</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>14.54479941614217</v>
+        <v>17.04267006477437</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.784349533528658</v>
+        <v>0.8463666987487969</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,11 +2160,11 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.6741844013516121</v>
+        <v>0.0322723005475438</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>513.5335058998604</v>
+        <v>628.5335058998604</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>24.35</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>57.94388846919635</v>
+        <v>57.94388845354209</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>9.584588928781043</v>
+        <v>9.584588985020078</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>1.636725192238518</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.0051943271898398</v>
+        <v>-0.0051943272089207</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1455</v>
+        <v>1558</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>513.1092342242713</v>
+        <v>619.1454996638605</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>9.98</v>
+        <v>102</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>59.53498321959289</v>
+        <v>64.96766375377308</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>25.75418242486687</v>
+        <v>28.58471068540949</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5551355879605779</v>
+        <v>0.916115359735214</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0358319063457071</v>
+        <v>0.5295414775330354</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1210</v>
+        <v>1308</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>509.5345709480135</v>
+        <v>605.5899071733322</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>52.4</v>
+        <v>14.1</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>37.5911920736918</v>
+        <v>57.12474438416283</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>30.81231199179391</v>
+        <v>20.56000228762188</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3454006513012727</v>
+        <v>1.247431842116818</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0139854583109271</v>
+        <v>0.1095931608551673</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1314</v>
+        <v>1319</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>498.0549412132126</v>
+        <v>604.7084122733056</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>8.16</v>
+        <v>81.7</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>55.16173359250031</v>
+        <v>58.91498745939985</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>16.39242345814451</v>
+        <v>32.75033684583475</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.463862551920224</v>
+        <v>0.4348574064896122</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0599375333774839</v>
+        <v>0.3739899472241368</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1529</v>
+        <v>1323</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>497.1563029057215</v>
+        <v>598.8679970401981</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>17.25</v>
+        <v>21.3</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>41.81974278719137</v>
+        <v>58.4254286820207</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>41.27587513976579</v>
+        <v>24.42510556557286</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.921382615602046</v>
+        <v>0.5240963375536716</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.1891747616816386</v>
+        <v>-0.0034598233384939</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1441</v>
+        <v>1402</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>496.6386713148378</v>
+        <v>587.9957277242853</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>9.15</v>
+        <v>28.4</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>56.25746650370488</v>
+        <v>53.45350837031049</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>17.04267006477437</v>
+        <v>20.97386354145592</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.8463666987487969</v>
+        <v>0.6560861205367812</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0322723005666227</v>
+        <v>0.1262052056476002</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1515</v>
+        <v>1110</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>493.9857363914263</v>
+        <v>582.6587268692977</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>35.4</v>
+        <v>15.95</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>56.1584607869195</v>
+        <v>49.28578505320474</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21.52302375358959</v>
+        <v>27.48927203485072</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2.907728979571857</v>
+        <v>0.5935171389281667</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.4929782233203183</v>
+        <v>-0.0338167836909752</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1409</v>
+        <v>1236</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>493.212255802579</v>
+        <v>581.4280635804374</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>25</v>
+        <v>25.7</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>56.0171560999666</v>
+        <v>63.16286781934747</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>9.510228337372324</v>
+        <v>22.24850285993803</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.262641643686421</v>
+        <v>0.8116792349057793</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,11 +2584,11 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.1644461358293885</v>
+        <v>0.0384754370097593</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>486.0644232906225</v>
+        <v>581.0644232906226</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>18.05</v>
@@ -2619,49 +2619,49 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>55.19625375198778</v>
+        <v>55.19625376197123</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>26.25147721962565</v>
+        <v>26.25147724556569</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>1.488053715327551</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0483633328696727</v>
+        <v>0.0483633328792082</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1110</v>
+        <v>1517</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>472.6587268692976</v>
+        <v>578.6356455797024</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>15.95</v>
+        <v>11.4</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>49.28578503607906</v>
+        <v>49.51971865741335</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>27.48927203453696</v>
+        <v>39.22910308850903</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5935171389281667</v>
+        <v>0.3124398616539581</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.0338167836718949</v>
+        <v>-0.0526787282549228</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1517</v>
+        <v>1532</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>468.6356455797024</v>
+        <v>564.1187156533222</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>11.4</v>
+        <v>22.95</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>49.51971873340131</v>
+        <v>58.37086050745021</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>39.22910297623711</v>
+        <v>20.59719842650347</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.3124398616539581</v>
+        <v>0.6260782806840363</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.0526787282453825</v>
+        <v>0.1315796499163966</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1217</v>
+        <v>1232</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>454.7049407704087</v>
+        <v>559.1810061715117</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>10</v>
+        <v>157</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>55.67933659401008</v>
+        <v>55.91890227743412</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>14.26590282520102</v>
+        <v>26.67084756569503</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.122606214917545</v>
+        <v>0.3799096892105097</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.011474716953866</v>
+        <v>0.0616712534339205</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1532</v>
+        <v>1315</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>454.1187156533224</v>
+        <v>552.2656825339631</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>22.95</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>58.37086062796852</v>
+        <v>52.3798184677493</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>20.59719846087633</v>
+        <v>33.23790369457498</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6260782806840363</v>
+        <v>0.8234504917286124</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.1315796499354767</v>
+        <v>0.0445102532846075</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1339</v>
+        <v>1521</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>451.5717433977729</v>
+        <v>536.9773774358318</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>43.1</v>
+        <v>26</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>37.75620241253027</v>
+        <v>58.42125799968823</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>17.7177198786498</v>
+        <v>15.29872235594085</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.544736304559319</v>
+        <v>0.6654039698780804</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.1544064621836754</v>
+        <v>0.0721855983609431</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1439</v>
+        <v>1455</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>449.1218521059699</v>
+        <v>533.1092342242713</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>29.2</v>
+        <v>9.98</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>59.52812196870116</v>
+        <v>59.53498330434181</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>10.09907979486589</v>
+        <v>25.7541824813394</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.2166378506015998</v>
+        <v>0.5551355879605779</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.0724696551740958</v>
+        <v>0.035831906334259</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1305</v>
+        <v>1216</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>446.0874818425227</v>
+        <v>530.114299992817</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>12.4</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>57.15365636566983</v>
+        <v>53.01720147340054</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>13.00116693317064</v>
+        <v>15.39528513983067</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.009742403428681</v>
+        <v>0.4955593563865499</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.1165132459876549</v>
+        <v>0.2010479917863942</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1308</v>
+        <v>1529</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>445.5899071733322</v>
+        <v>517.1563029057215</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>14.1</v>
+        <v>17.25</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>57.12474440831253</v>
+        <v>41.81974291307746</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>20.56000227827897</v>
+        <v>41.27587511753824</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.247431842116818</v>
+        <v>1.921382615602046</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1095931608742471</v>
+        <v>0.1891747614908445</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1472</v>
+        <v>1304</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>430.2283901260852</v>
+        <v>513.9972711127966</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>89.5</v>
+        <v>12.4</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>52.4652696108458</v>
+        <v>53.89418646281338</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>4.749965516826922</v>
+        <v>12.6276129635058</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2.1051979431262</v>
+        <v>1.463186307531366</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.2061205087222832</v>
+        <v>0.1082808340729154</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1521</v>
+        <v>1233</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>426.977377435832</v>
+        <v>511.5601070515471</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>26</v>
+        <v>28.45</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>58.42125805507136</v>
+        <v>53.22795285173873</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>15.29872234151313</v>
+        <v>23.05679040903112</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6654039698780804</v>
+        <v>0.5307939278952717</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0721855983991035</v>
+        <v>0.0504967091845147</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1101</v>
+        <v>1210</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>425.4283909017288</v>
+        <v>509.5345709480135</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>24.1</v>
+        <v>52.4</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,49 +3202,49 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>47.52450621113088</v>
+        <v>37.59119201214671</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>24.03082413531267</v>
+        <v>30.81231198454362</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.022903618509982</v>
+        <v>0.3454006513012727</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0207682665559877</v>
+        <v>0.0139854583109271</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1216</v>
+        <v>1414</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>420.1142999928171</v>
+        <v>505.0830989344101</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>77.09999999999999</v>
+        <v>19.25</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>53.01720155551028</v>
+        <v>49.51072279072875</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>15.39528508602222</v>
+        <v>22.24146502424864</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4955593563865499</v>
+        <v>0.8984240093391235</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.2010479915192886</v>
+        <v>-0.1147338283491217</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1321</v>
+        <v>1340</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>415.5332677178819</v>
+        <v>505.0139115907801</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>33.75</v>
+        <v>5.25</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>71.03594599215882</v>
+        <v>52.18635348706095</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>17.48866669112635</v>
+        <v>15.93522912845336</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.02640905040821</v>
+        <v>0.7424161527419383</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.1659868246097849</v>
+        <v>0.0311803348437438</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1560</v>
+        <v>1524</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>402.9662994313688</v>
+        <v>491.2586541854902</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>690</v>
+        <v>27.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.16190425003825</v>
+        <v>55.06871273112017</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>8.52460143307702</v>
+        <v>16.957759737318</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5059095414072045</v>
+        <v>1.333817500740585</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-1.760859611539818</v>
+        <v>0.1332508718538944</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1233</v>
+        <v>1435</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>396.5601070515471</v>
+        <v>488.9201222713194</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>28.45</v>
+        <v>23</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>53.22795292865551</v>
+        <v>49.17731265303343</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>23.05679040903112</v>
+        <v>6.959878028600738</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5307939278952717</v>
+        <v>0.3775557756646561</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0504967091845147</v>
+        <v>-0.2049373975836037</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1414</v>
+        <v>1309</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>395.0830989344101</v>
+        <v>472.4679302535306</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>19.25</v>
+        <v>13.4</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>49.51072268310836</v>
+        <v>50.88516500836538</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>22.24146507637928</v>
+        <v>14.08313012532354</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8984240093391235</v>
+        <v>1.593071487497663</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.1147338281856292</v>
+        <v>0.1458172114473906</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1516</v>
+        <v>1436</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>387.7500267739493</v>
+        <v>464.5398488933814</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>14.9</v>
+        <v>39.15</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>49.93908058789813</v>
+        <v>52.37293285340378</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>31.19699367081684</v>
+        <v>22.39038654944613</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.391658614073199</v>
+        <v>0.4443671632661977</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.3533175779984336</v>
+        <v>0.508425949492699</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1524</v>
+        <v>1215</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>381.2586541854905</v>
+        <v>463.3688998838032</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>27.5</v>
+        <v>108.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,49 +3573,49 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>55.06871263249713</v>
+        <v>47.38124321113302</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>16.95775974945317</v>
+        <v>22.77690072486306</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.333817500740585</v>
+        <v>0.675631089345322</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.1332508719969898</v>
+        <v>0.3636141136190776</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1435</v>
+        <v>1526</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>378.9201222713194</v>
+        <v>460.3601378161754</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>23</v>
+        <v>16.4</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>49.17733176190527</v>
+        <v>45.03726364669819</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>6.959880584846824</v>
+        <v>27.88454525728624</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.3775557756646561</v>
+        <v>0.1520366616816091</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.2049374920858256</v>
+        <v>-0.2576587357739771</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1417</v>
+        <v>1339</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>369.4856206793579</v>
+        <v>451.5717433977729</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>8.279999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>45.51219752086852</v>
+        <v>37.75620243444362</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>14.65144220717262</v>
+        <v>17.71771998979329</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.248929605151844</v>
+        <v>2.544736304559319</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0141957783294906</v>
+        <v>-0.154406462298153</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1437</v>
+        <v>1472</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>365.0749372778814</v>
+        <v>450.2283901260852</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>32.15</v>
+        <v>89.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>61.81245431344385</v>
+        <v>52.46526962973237</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>21.30679489293765</v>
+        <v>4.74996553684811</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.1056108697321882</v>
+        <v>2.1051979431262</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.08450400877479269</v>
+        <v>0.2061205087222832</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1530</v>
+        <v>1439</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>362.9739255882527</v>
+        <v>449.1218521059699</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>52.98044639230364</v>
+        <v>59.52812189813358</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>13.86290800610885</v>
+        <v>10.09907975095633</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3033545349775565</v>
+        <v>0.2166378506015998</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.1183613995164091</v>
+        <v>-0.0724696551359415</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1526</v>
+        <v>1219</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>360.3601378161754</v>
+        <v>438.6862597634391</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>16.4</v>
+        <v>11.8</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>45.0372635869661</v>
+        <v>60.57140065357652</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>27.88454507105497</v>
+        <v>20.85210059521859</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.1520366616816091</v>
+        <v>0.8721070508720541</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.2576587356690425</v>
+        <v>0.1343609710557683</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1525</v>
+        <v>1203</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>357.8806355006489</v>
+        <v>429.5771365991353</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>47.30256623769555</v>
+        <v>52.00200945516711</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>23.12065079317052</v>
+        <v>18.0892338283016</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6718433146851722</v>
+        <v>0.3526968525598851</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.1325292727484193</v>
+        <v>-0.0235764918628772</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1446</v>
+        <v>1456</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>357.8261325628501</v>
+        <v>428.6533636715181</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>13.6</v>
+        <v>13.9</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>33.80520370468159</v>
+        <v>50.71003594489649</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>36.78982367679415</v>
+        <v>20.84143663144744</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.601338464932709</v>
+        <v>0.9639121873597092</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0506208678836145</v>
+        <v>0.0174717775889701</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1436</v>
+        <v>1101</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>354.5398488933814</v>
+        <v>425.4283909017289</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>39.15</v>
+        <v>24.1</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,49 +3997,49 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>52.37293298785115</v>
+        <v>47.52450624916289</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>22.39038657572493</v>
+        <v>24.03082417157536</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.4443671632661977</v>
+        <v>1.022903618509982</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.5084259493972948</v>
+        <v>-0.0207682666227689</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1215</v>
+        <v>1560</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>353.3688998838032</v>
+        <v>422.9662994313689</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>108.5</v>
+        <v>690</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>47.38124307562802</v>
+        <v>50.161904281741</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>22.77690070809893</v>
+        <v>8.524601486545482</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.675631089345322</v>
+        <v>0.5059095414072045</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.3636141139052856</v>
+        <v>-1.760859613352343</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1452</v>
+        <v>1225</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>342.5856776620196</v>
+        <v>398.6164436273019</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>11.45</v>
+        <v>25.85</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.06256956032294</v>
+        <v>53.7673723403434</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>13.06579518169605</v>
+        <v>28.92503026002736</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.7038890685261466</v>
+        <v>0.6707381113908673</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0009741247307984</v>
+        <v>0.2878977135278727</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1341</v>
+        <v>1325</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>337.9843530905421</v>
+        <v>396.4387504327746</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>60.3</v>
+        <v>26.3</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>53.57796697820386</v>
+        <v>51.10231760172835</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>15.24246084292179</v>
+        <v>27.06800079267233</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.304184517870767</v>
+        <v>0.5654755612581515</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.0414772281197954</v>
+        <v>-0.0516000134661702</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1477</v>
+        <v>1417</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>325.1236390917323</v>
+        <v>389.4856206793579</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>198.5</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>36.0648191135553</v>
+        <v>45.51219749550869</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>22.45584220840321</v>
+        <v>14.65144220484388</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.3942011486363544</v>
+        <v>1.248929605151844</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-1.434203550718777</v>
+        <v>0.0141957783256762</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1340</v>
+        <v>1522</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>315.0139115907802</v>
+        <v>388.1949687755841</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>5.25</v>
+        <v>28.2</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.18635334769636</v>
+        <v>47.76435306845928</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>15.93522912845336</v>
+        <v>13.14963641721298</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7424161527419383</v>
+        <v>0.7501184935500939</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0311803348876271</v>
+        <v>0.1022623831843727</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1203</v>
+        <v>1516</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>314.5771365991353</v>
+        <v>387.7500267739491</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>46</v>
+        <v>14.9</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>52.00200937575985</v>
+        <v>49.93908060798268</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>18.08923376741014</v>
+        <v>31.19699376962215</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.3526968525598851</v>
+        <v>1.391658614073199</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0235764917484004</v>
+        <v>0.3533175779030387</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1456</v>
+        <v>1447</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>313.653363671518</v>
+        <v>386.0412881885865</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>13.9</v>
+        <v>6.9</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>50.71003593440744</v>
+        <v>45.94210211270172</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>20.84143665787149</v>
+        <v>11.94578602858016</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.9639121873597092</v>
+        <v>0.6524417139142812</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0174717775698907</v>
+        <v>0.0132245506410483</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1219</v>
+        <v>1530</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>298.6862597634391</v>
+        <v>382.9739255882526</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>11.8</v>
+        <v>29.3</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>60.57140059552757</v>
+        <v>52.98044646756505</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>20.85210045132467</v>
+        <v>13.86290821996147</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.8721070508720541</v>
+        <v>0.3033545349775565</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.1343609711034679</v>
+        <v>0.1183613993446965</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1342</v>
+        <v>1419</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>293.4806067770513</v>
+        <v>380.8884245276381</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>104</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>49.00579857044411</v>
+        <v>53.04981829663825</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>19.31175031775299</v>
+        <v>15.67117828664784</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6087925651866199</v>
+        <v>0.5589504453391871</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.4575842521938857</v>
+        <v>0.2105071006908158</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1447</v>
+        <v>1536</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>291.0412881885864</v>
+        <v>380.5005512145251</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>6.9</v>
+        <v>51.1</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45.9421021070545</v>
+        <v>53.8253106517837</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>11.94578603579033</v>
+        <v>12.70663938278753</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6524417139142812</v>
+        <v>0.9049617381809644</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0132245506524968</v>
+        <v>-0.0193017105544434</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1325</v>
+        <v>1569</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>286.4387504327746</v>
+        <v>379.8285094572629</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>26.3</v>
+        <v>44.75</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>51.10231749971954</v>
+        <v>54.72023603315508</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>27.06800071003793</v>
+        <v>18.85433808076684</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5654755612581515</v>
+        <v>0.6541543672155448</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.051600013275377</v>
+        <v>0.4459527582475405</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1522</v>
+        <v>1525</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>278.194968775584</v>
+        <v>377.880635500649</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>28.2</v>
+        <v>67</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>47.7643529542862</v>
+        <v>47.30256606741687</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>13.1496364477646</v>
+        <v>23.12065070189471</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.7501184935500939</v>
+        <v>0.6718433146851722</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.102262383375169</v>
+        <v>-0.1325292726721023</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1539</v>
+        <v>1438</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>276.2418435697108</v>
+        <v>375.2583721387374</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>15.65</v>
+        <v>22.35</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>41.01996153896666</v>
+        <v>50.12680843426422</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>13.15443806901662</v>
+        <v>9.101083791194707</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.6699210095280126</v>
+        <v>1.139037123129971</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0523577588923235</v>
+        <v>-0.024571323976427</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1536</v>
+        <v>1568</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>270.5005512145251</v>
+        <v>374.3051892628437</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>51.1</v>
+        <v>29.05</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>53.82531053454469</v>
+        <v>46.82791357308473</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>12.70663921793094</v>
+        <v>13.00149674983118</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.9049617381809644</v>
+        <v>0.4542662583168954</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.0193017100393033</v>
+        <v>0.284186887798144</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1231</v>
+        <v>1466</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>269.6473648693077</v>
+        <v>371.9805135084604</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>81</v>
+        <v>16.1</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>41.255208239394</v>
+        <v>47.4418584688524</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>15.56824051396968</v>
+        <v>12.28123396445893</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.42569742307156</v>
+        <v>0.3595080614518063</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.2042868479745074</v>
+        <v>-0.055425416019636</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1419</v>
+        <v>1437</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>265.8884245276381</v>
+        <v>365.0749372778814</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>66.40000000000001</v>
+        <v>32.15</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>53.04981826593218</v>
+        <v>61.81245432011329</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15.67117820015775</v>
+        <v>21.30679502536302</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5589504453391871</v>
+        <v>0.1056108697321882</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.2105071009579129</v>
+        <v>0.0845040087843319</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1438</v>
+        <v>1446</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>265.2583721387374</v>
+        <v>357.8261325628501</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>22.35</v>
+        <v>13.6</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>50.12680884824096</v>
+        <v>33.80520356473703</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>9.101083847763034</v>
+        <v>36.78982378009897</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.139037123129971</v>
+        <v>0.601338464932709</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0245713238905706</v>
+        <v>0.0506208678454547</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1569</v>
+        <v>1423</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>264.8285094572629</v>
+        <v>354.1211354568531</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>44.75</v>
+        <v>35.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>54.72023593641209</v>
+        <v>45.11792480341335</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>18.85433808181002</v>
+        <v>12.46578623725393</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.6541543672155448</v>
+        <v>0.900725259299696</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.4459527586863677</v>
+        <v>0.1041535099025859</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1568</v>
+        <v>1452</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>264.3051892628437</v>
+        <v>342.5856776620196</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>29.05</v>
+        <v>11.45</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>46.82791355801104</v>
+        <v>51.06256964670875</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>13.00149677938314</v>
+        <v>13.06579523634484</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.4542662583168954</v>
+        <v>0.7038890685261466</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.2841868879030819</v>
+        <v>0.0009741246926389001</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1304</v>
+        <v>1341</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>263.9972711127966</v>
+        <v>337.9843530905421</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>12.4</v>
+        <v>60.3</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>53.8941864859245</v>
+        <v>53.57796697881169</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>12.62761294575035</v>
+        <v>15.24246084315923</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.463186307531366</v>
+        <v>1.304184517870767</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.1082808340824558</v>
+        <v>-0.0414772281388691</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1466</v>
+        <v>1307</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>261.9805135084604</v>
+        <v>337.9015894676818</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>16.1</v>
+        <v>30.95</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>47.44185836869783</v>
+        <v>45.96614724648314</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.28123386206922</v>
+        <v>22.78302076825805</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.3595080614518063</v>
+        <v>0.9308426908173834</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.055425415933779</v>
+        <v>0.0937778473489479</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1225</v>
+        <v>1418</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>258.6164436273019</v>
+        <v>336.0921660723747</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>25.85</v>
+        <v>17.95</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>53.76737232688697</v>
+        <v>47.52088169634653</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>28.92503025617303</v>
+        <v>16.79948763738976</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6707381113908673</v>
+        <v>0.226142935571449</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.2878977137091255</v>
+        <v>0.0131379379707805</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1527</v>
+        <v>1220</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>256.3361657701667</v>
+        <v>332.0578947758117</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>32.75</v>
+        <v>10.9</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>45.59137791662098</v>
+        <v>33.86390026088873</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>12.59884316142152</v>
+        <v>30.62284807516011</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.3134320941568869</v>
+        <v>0.8332773152976943</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.017282443056245</v>
+        <v>0.0030694516352233</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1533</v>
+        <v>1201</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>250.7762501415888</v>
+        <v>327.9201562074415</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>31.95</v>
+        <v>12.2</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>43.97649983586959</v>
+        <v>45.26189731444725</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>29.1561781890033</v>
+        <v>9.147066790553549</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5898854635078266</v>
+        <v>1.182080256148928</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.1323255816086086</v>
+        <v>0.008324270545188899</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1467</v>
+        <v>1477</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>244.1769140057472</v>
+        <v>325.1236390917322</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>8.359999999999999</v>
+        <v>198.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>42.34164380760892</v>
+        <v>36.06481904591381</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>14.13624909719531</v>
+        <v>22.45584221615454</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.3996345058840297</v>
+        <v>0.3942011486363544</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.1021304480067155</v>
+        <v>-1.434203550051004</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1423</v>
+        <v>1467</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>244.1211354568531</v>
+        <v>319.1769140057472</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>35.5</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45.11793765217993</v>
+        <v>42.34164382109189</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>12.46578862838711</v>
+        <v>14.13624912364893</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.900725259299696</v>
+        <v>0.3996345058840297</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.1041535027191761</v>
+        <v>-0.102130448023887</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1541</v>
+        <v>1468</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>243.7614280814726</v>
+        <v>318.6446236453777</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>21.85</v>
+        <v>13.3</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>51.79486872701733</v>
+        <v>51.41951210015272</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>21.21617836260641</v>
+        <v>16.92646580005255</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.973212751331844</v>
+        <v>1.248669781309682</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0119047409357416</v>
+        <v>-0.0554437879397978</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1309</v>
+        <v>1460</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>237.4679302535306</v>
+        <v>301.7615700519323</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>13.4</v>
+        <v>6.64</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>50.88516500836538</v>
+        <v>44.56963524535615</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>14.08313010436309</v>
+        <v>15.60301851681626</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.593071487497663</v>
+        <v>0.7611549414450621</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.1458172114760083</v>
+        <v>0.0261482690491163</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1537</v>
+        <v>1342</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>235.2079070131782</v>
+        <v>293.4806067770514</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>119.5</v>
+        <v>104</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>27.17825639526966</v>
+        <v>49.0057985900399</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>25.66170892478453</v>
+        <v>19.31175041002</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.8621527034698577</v>
+        <v>0.6087925651866199</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.769526984334244</v>
+        <v>0.4575842519458426</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1465</v>
+        <v>1103</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>234.6603434674735</v>
+        <v>282.0448838844159</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>11.95</v>
+        <v>13.2</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>38.15133908775708</v>
+        <v>48.2928441128312</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>23.41442693146699</v>
+        <v>12.02709835361247</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>2.166034346747346</v>
+        <v>0.7703021959055212</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0134470241047605</v>
+        <v>0.0264938907052271</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1256</v>
+        <v>1539</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>231.0412020788953</v>
+        <v>276.2418435697107</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>183</v>
+        <v>15.65</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>52.58420359176477</v>
+        <v>41.01996150611962</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>10.0526292203077</v>
+        <v>13.15443809857755</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.230200478667444</v>
+        <v>0.6699210095280126</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.7812902370583998</v>
+        <v>-0.052357758959101</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1473</v>
+        <v>1533</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>229.2697341788603</v>
+        <v>270.7762501415888</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>20.1</v>
+        <v>31.95</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>52.81802797476134</v>
+        <v>43.97649989620945</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>7.914264912393179</v>
+        <v>29.15617825484509</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.409334391429422</v>
+        <v>0.5898854635078266</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0330052993979988</v>
+        <v>0.1323255815227508</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1540</v>
+        <v>1231</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>228.3503227556978</v>
+        <v>269.6473648693077</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>19.35</v>
+        <v>81</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>40.4327457872205</v>
+        <v>41.255208239394</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>22.64121165068752</v>
+        <v>15.56824046730124</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.3335105938245222</v>
+        <v>0.42569742307156</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0780012422889205</v>
+        <v>0.2042868478791082</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1307</v>
+        <v>1444</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>227.9015894676817</v>
+        <v>267.4444539113702</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>30.95</v>
+        <v>7.16</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45.96614717969703</v>
+        <v>43.86503819729204</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>22.78302075452513</v>
+        <v>16.79865677811395</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.9308426908173834</v>
+        <v>0.8277984963144065</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0937778474538855</v>
+        <v>0.0186114260512539</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1451</v>
+        <v>1541</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>226.6482250309298</v>
+        <v>263.7614280814726</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>17.3</v>
+        <v>21.85</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>46.70318442450408</v>
+        <v>51.79486870671153</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>17.68147696839782</v>
+        <v>21.21617835940706</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.9145895382661982</v>
+        <v>0.973212751331844</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0302831773710095</v>
+        <v>0.011904740916662</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1418</v>
+        <v>1527</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>226.0921660723747</v>
+        <v>256.3361657701664</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>17.95</v>
+        <v>32.75</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>47.52088162140632</v>
+        <v>45.59137797909239</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>16.79948760966889</v>
+        <v>12.59884316142152</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.226142935571449</v>
+        <v>0.3134320941568869</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0131379379898577</v>
+        <v>0.0172824429799257</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1220</v>
+        <v>1465</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>222.0578947758117</v>
+        <v>254.6603434674735</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>10.9</v>
+        <v>11.95</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>33.86390039761827</v>
+        <v>38.15133910412787</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>30.62284807516011</v>
+        <v>23.41442694999169</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.8332773152976943</v>
+        <v>2.166034346747346</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0030694516352233</v>
+        <v>-0.0134470241238402</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1201</v>
+        <v>1540</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>217.9201562074415</v>
+        <v>248.3503227556978</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>12.2</v>
+        <v>19.35</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45.26189728456196</v>
+        <v>40.43274580672653</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>9.147066713447249</v>
+        <v>22.64121169466294</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.182080256148928</v>
+        <v>0.3335105938245222</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0083242705642662</v>
+        <v>0.0780012422126016</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1213</v>
+        <v>1464</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>215.9197056187834</v>
+        <v>245.824809009148</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>7.34</v>
+        <v>10.35</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>52.06911752351514</v>
+        <v>52.43372236779922</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>11.61646571185798</v>
+        <v>10.22916452692041</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.0421044685673786</v>
+        <v>0.6808964292679309</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.116273027005921</v>
+        <v>0.0219631831898868</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1468</v>
+        <v>1218</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>208.6446236453778</v>
+        <v>242.1733322869678</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>13.3</v>
+        <v>14.6</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>51.41951216121668</v>
+        <v>49.34114752030045</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>16.92646571638076</v>
+        <v>20.76277879024412</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.248669781309682</v>
+        <v>1.246193797721653</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0554437879302579</v>
+        <v>0.2440314889047092</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1103</v>
+        <v>1537</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>207.044883884416</v>
+        <v>235.2079070131782</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>13.2</v>
+        <v>119.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>48.29284391240597</v>
+        <v>27.17825637765094</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.02709842210624</v>
+        <v>25.66170899770711</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.7703021959055212</v>
+        <v>0.8621527034698577</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0264938907433857</v>
+        <v>-0.769526984429632</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1460</v>
+        <v>1256</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>206.7615700519324</v>
+        <v>231.0412020788953</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>6.64</v>
+        <v>183</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>44.56963516990084</v>
+        <v>52.5842036225857</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>15.60301854969874</v>
+        <v>10.05262927249544</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.7611549414450621</v>
+        <v>1.230200478667444</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0261482690739189</v>
+        <v>0.7812902364859873</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1338</v>
+        <v>1473</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>203.1104723445576</v>
+        <v>229.2697341788603</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>14.35</v>
+        <v>20.1</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>30.97814332600671</v>
+        <v>52.81802820488299</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>44.08691583245216</v>
+        <v>7.914264919837732</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5000343902606782</v>
+        <v>1.409334391429422</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0032104874765012</v>
+        <v>0.0330052993407597</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1476</v>
+        <v>1451</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>202.9504925246148</v>
+        <v>226.6482250309298</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>314</v>
+        <v>17.3</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>39.57797668324695</v>
+        <v>46.70318456553652</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>19.18561653719144</v>
+        <v>17.68147706512403</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.568626126177995</v>
+        <v>0.9145895382661982</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-1.415023233032557</v>
+        <v>-0.0302831773900889</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1457</v>
+        <v>1463</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>200.3062477471268</v>
+        <v>219.8128154736693</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>14.4</v>
+        <v>17.4</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>52.04199174402577</v>
+        <v>39.93973802825354</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>14.80493562150103</v>
+        <v>13.91827061867623</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.190380128919945</v>
+        <v>1.004326628311809</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0132103117730387</v>
+        <v>-0.0286853510528572</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1463</v>
+        <v>1213</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>199.8128154736693</v>
+        <v>215.9197056187835</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>17.4</v>
+        <v>7.34</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>39.93973789839555</v>
+        <v>52.06911752690965</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>13.91827049737908</v>
+        <v>11.61646571099289</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.004326628311809</v>
+        <v>0.0421044685673786</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0286853509670017</v>
+        <v>-0.1162730270250002</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1108</v>
+        <v>1443</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>195.8943802467378</v>
+        <v>207.3672934854657</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>11.75</v>
+        <v>25</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>35.50154156174877</v>
+        <v>50.56473382504086</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>53.45064302107066</v>
+        <v>7.990720678470812</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.4878641341742768</v>
+        <v>0.3875785059536203</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0508059784061113</v>
+        <v>0.2975259707864945</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1444</v>
+        <v>1227</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>192.4444539113702</v>
+        <v>204.955588935053</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>7.16</v>
+        <v>28.85</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,49 +6541,49 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>43.86503819077189</v>
+        <v>45.84219454015288</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>16.79865670142316</v>
+        <v>11.97217593976002</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.8277984963144065</v>
+        <v>0.5503085013778826</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0186114260684255</v>
+        <v>0.0109447407139034</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1109</v>
+        <v>1338</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>181.6723546720198</v>
+        <v>203.1104723445576</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>13.6</v>
+        <v>14.35</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>44.0050712132686</v>
+        <v>30.97814338649711</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>26.85694045846803</v>
+        <v>44.08691578857228</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.8555738130898188</v>
+        <v>0.5000343902606782</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0393887720840056</v>
+        <v>-0.0032104875337382</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1506</v>
+        <v>1476</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>181.2747574529427</v>
+        <v>202.9504925246153</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>10.1</v>
+        <v>314</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>42.17448888370667</v>
+        <v>39.577976029181</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>12.76104641880572</v>
+        <v>19.1856167079519</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.269115692375254</v>
+        <v>0.568626126177995</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0135510389951827</v>
+        <v>-1.4150232257824</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1324</v>
+        <v>1457</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>177.5786255967778</v>
+        <v>200.3062477471269</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>10.2</v>
+        <v>14.4</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>54.65060320285251</v>
+        <v>52.04199179482409</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>14.98964297323388</v>
+        <v>14.80493553431624</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.100975651782881</v>
+        <v>1.190380128919945</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.024350666222556</v>
+        <v>0.0132103117348786</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1410</v>
+        <v>1324</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>175.7504241823102</v>
+        <v>197.5786255967778</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>24.75</v>
+        <v>10.2</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>38.92870469909463</v>
+        <v>54.65060352269351</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>12.24796180602441</v>
+        <v>14.98964304879268</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.5639769665171851</v>
+        <v>1.100975651782881</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.1139439048547311</v>
+        <v>0.0243506661748574</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1538</v>
+        <v>1108</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>174.9083316055842</v>
+        <v>195.8943802467378</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>45.9480137095486</v>
+        <v>35.50154158272981</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>10.69589533713516</v>
+        <v>53.45064301613278</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.8343470483005366</v>
+        <v>0.4878641341742768</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.107053035534707</v>
+        <v>0.0508059783870316</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1432</v>
+        <v>1109</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>167.7800782846264</v>
+        <v>181.6723546720198</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>15.05</v>
+        <v>13.6</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>43.32283430557403</v>
+        <v>44.00507123964953</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>14.39006329831502</v>
+        <v>26.85694042289117</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.7485247071208475</v>
+        <v>0.8555738130898188</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0178500300433207</v>
+        <v>0.0393887720744655</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1218</v>
+        <v>1506</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>167.1733322869678</v>
+        <v>181.2747574529427</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>14.6</v>
+        <v>10.1</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>49.34114747982508</v>
+        <v>42.17448884469079</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>20.76277854720129</v>
+        <v>12.76104636878778</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.246193797721653</v>
+        <v>1.269115692375254</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.2440314891145834</v>
+        <v>-0.0135510389951827</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1454</v>
+        <v>1410</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>165.563727449242</v>
+        <v>175.7504241823102</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>12.55</v>
+        <v>24.75</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>47.80479992715701</v>
+        <v>38.92870460043694</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>29.0721643417549</v>
+        <v>12.24796184005522</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.2882285993008698</v>
+        <v>0.5639769665171851</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0119218101022917</v>
+        <v>-0.113943904950128</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1104</v>
+        <v>1538</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>159.9723322032152</v>
+        <v>174.9083316055842</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>26.6</v>
+        <v>0</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>46.47170148978603</v>
+        <v>45.94801338254422</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>9.451405638401219</v>
+        <v>10.69589534759839</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.7857770877633834</v>
+        <v>0.8343470483005366</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0439361300432624</v>
+        <v>-0.1070530357350412</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1445</v>
+        <v>1432</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>139.5609441944746</v>
+        <v>167.7800782846264</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>10.3</v>
+        <v>15.05</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>41.88404213274865</v>
+        <v>43.32283437895746</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>13.8056274109092</v>
+        <v>14.39006330402557</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.280376465355255</v>
+        <v>0.7485247071208475</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0433100949890286</v>
+        <v>0.0178500300242419</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1464</v>
+        <v>1454</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>135.824809009148</v>
+        <v>165.5637274492443</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>10.35</v>
+        <v>12.55</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>52.43372240766796</v>
+        <v>47.80479990610098</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>10.22916449040414</v>
+        <v>29.07216436654078</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.6808964292679309</v>
+        <v>0.2882285993008698</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.021963183199427</v>
+        <v>-0.0119218101213721</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1413</v>
+        <v>1104</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>135.3896925045341</v>
+        <v>159.9723322032152</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>9.32</v>
+        <v>26.6</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,25 +7177,25 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>46.989151417595</v>
+        <v>46.47170161598428</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>8.294042210754737</v>
+        <v>9.451405636800066</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.2454984332959506</v>
+        <v>0.7857770877633834</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M127" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0012591542340399</v>
+        <v>0.0439361299764818</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1227</v>
+        <v>1445</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>129.955588935053</v>
+        <v>159.5609441944746</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>28.85</v>
+        <v>10.3</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,16 +7230,16 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>45.84219449876085</v>
+        <v>41.88404213274865</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>11.97217598982132</v>
+        <v>13.8056274816972</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.5503085013778826</v>
+        <v>1.280376465355255</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L128" s="2" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.0109447407425213</v>
+        <v>0.0433100949699482</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>123.7186108166068</v>
+        <v>143.7186108166067</v>
       </c>
       <c r="E129" s="2" t="n">
         <v>26.6</v>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>51.04633197210077</v>
+        <v>51.04633202040282</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>15.80623595114323</v>
+        <v>15.80623595190039</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.1335348769699253</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0552602675667946</v>
+        <v>0.0552602673950798</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>119.8950387802171</v>
+        <v>139.8950387802171</v>
       </c>
       <c r="E130" s="2" t="n">
         <v>10</v>
@@ -7336,16 +7336,16 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>43.34104218466867</v>
+        <v>43.34104251574255</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>15.93653691725307</v>
+        <v>15.93653676362656</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.9408121742683898</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.0064656170115041</v>
+        <v>0.0064656169351844</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7364,21 +7364,21 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>1512</v>
+        <v>1413</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>107.0835476206309</v>
+        <v>135.3896925045341</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>6.46</v>
+        <v>9.32</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>38.5657168503997</v>
+        <v>46.98915137901632</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>9.951428009882489</v>
+        <v>8.294042210754736</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>1.430709662294085</v>
+        <v>0.2454984332959506</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.0058661608733891</v>
+        <v>-0.0012591542435799</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>1535</v>
+        <v>1512</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>99.21623860269018</v>
+        <v>107.0835476206311</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>46</v>
+        <v>6.46</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>42.16015911473554</v>
+        <v>38.56571636733419</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>12.11707242618289</v>
+        <v>9.951428128321927</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.9717632423875529</v>
+        <v>1.430709662294085</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>0</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.1483608899981927</v>
+        <v>-0.0058661607169373</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7470,21 +7470,21 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>1443</v>
+        <v>1535</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>97.36729348546568</v>
+        <v>99.21623860269018</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,13 +7495,13 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>50.56473383569804</v>
+        <v>42.16015913137029</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>7.990720677009345</v>
+        <v>12.11707242618288</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.3875785059536203</v>
+        <v>0.9717632423875529</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>0</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.2975259707769577</v>
+        <v>0.1483608899791074</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
